--- a/output/pdf_financials_xlsx/STR.H.xlsx
+++ b/output/pdf_financials_xlsx/STR.H.xlsx
@@ -3453,16 +3453,16 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.461057</v>
+        <v>0.057013</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.097013</v>
+        <v>0.057013</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.09575500000000001</v>
+        <v>0.055755</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0</v>
+        <v>0.001875</v>
       </c>
       <c r="F48" s="3" t="n">
         <v>0</v>
@@ -3524,8 +3524,10 @@
       <c r="D49" s="3" t="n">
         <v>0.488955</v>
       </c>
-      <c r="E49" s="3" t="n">
-        <v>0.001875</v>
+      <c r="E49" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F49" s="1" t="inlineStr">
         <is>
@@ -4341,7 +4343,7 @@
         <v>0</v>
       </c>
       <c r="E61" s="3" t="n">
-        <v>0.054999</v>
+        <v>0</v>
       </c>
       <c r="F61" s="3" t="n">
         <v>0</v>
@@ -4403,8 +4405,10 @@
       <c r="D62" s="3" t="n">
         <v>0.280473</v>
       </c>
-      <c r="E62" s="3" t="n">
-        <v>0.054999</v>
+      <c r="E62" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F62" s="1" t="inlineStr">
         <is>
@@ -6412,34 +6416,34 @@
         <v>3.428663</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>3.428663</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>3.428663</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>3.428663</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>3.428662</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>3.428662</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>3.428662</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>3.428662</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>3.428662</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>3.428662</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>3.428662</v>
       </c>
       <c r="S92" s="1" t="inlineStr">
         <is>
@@ -9934,7 +9938,11 @@
           <t>Share-based payment reserve (Note 5)</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>-</t>
@@ -10914,7 +10922,11 @@
           <t>Share-based payment reserve (Note 6)</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>-</t>
@@ -13022,7 +13034,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>CurrentAssets</t>
+          <t>OtherCurrentAssets</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -13672,7 +13684,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>CurrentAssets</t>
+          <t>OtherCurrentAssets</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -16024,7 +16036,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>CurrentAssets</t>
+          <t>OtherCurrentAssets</t>
         </is>
       </c>
       <c r="E66" s="5" t="n">

--- a/output/pdf_financials_xlsx/STR.H.xlsx
+++ b/output/pdf_financials_xlsx/STR.H.xlsx
@@ -1081,10 +1081,10 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>3.8e-05</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.026918</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>0</v>
@@ -2136,10 +2136,10 @@
         <v>-1.676561</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.676561</v>
+        <v>-1.676599</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>3.332285</v>
+        <v>3.305367</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>-0.051206</v>
@@ -2262,10 +2262,10 @@
         <v>-1.601493</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.605288</v>
+        <v>-1.605326</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>3.332285</v>
+        <v>3.305367</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>-0.051206</v>
@@ -2325,7 +2325,7 @@
         <v>-49.57938603022328</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-50.87427845960674</v>
+        <v>-50.87548274356168</v>
       </c>
       <c r="E30" s="1" t="inlineStr">
         <is>
@@ -2571,7 +2571,7 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.364044</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>0.364044</v>
@@ -2592,34 +2592,34 @@
         <v>0.000851</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.020483</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.028341</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.003256</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.000476</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>6.7e-05</v>
       </c>
       <c r="N34" s="3" t="n">
         <v>0</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.031622</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.004699</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.030296</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>9.500000000000001e-05</v>
       </c>
       <c r="S34" s="1" t="inlineStr">
         <is>
@@ -2697,7 +2697,7 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.364044</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>0.364044</v>
@@ -2718,34 +2718,34 @@
         <v>0.000851</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.020483</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.028341</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.003256</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.000476</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>6.7e-05</v>
       </c>
       <c r="N36" s="3" t="n">
         <v>0</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.031622</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.004699</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.030296</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>9.500000000000001e-05</v>
       </c>
       <c r="S36" s="1" t="inlineStr">
         <is>
@@ -3453,16 +3453,16 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.057013</v>
+        <v>0.097013</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.057013</v>
+        <v>0.097013</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.055755</v>
+        <v>0.09575500000000001</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.001875</v>
+        <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
         <v>0</v>
@@ -3524,10 +3524,8 @@
       <c r="D49" s="3" t="n">
         <v>0.488955</v>
       </c>
-      <c r="E49" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E49" s="3" t="n">
+        <v>0.001875</v>
       </c>
       <c r="F49" s="1" t="inlineStr">
         <is>
@@ -4343,7 +4341,7 @@
         <v>0</v>
       </c>
       <c r="E61" s="3" t="n">
-        <v>0</v>
+        <v>0.054999</v>
       </c>
       <c r="F61" s="3" t="n">
         <v>0</v>
@@ -4405,10 +4403,8 @@
       <c r="D62" s="3" t="n">
         <v>0.280473</v>
       </c>
-      <c r="E62" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E62" s="3" t="n">
+        <v>0.054999</v>
       </c>
       <c r="F62" s="1" t="inlineStr">
         <is>
@@ -9378,7 +9374,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -13034,7 +13030,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -13684,7 +13680,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -16036,7 +16032,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E66" s="5" t="n">
@@ -31114,7 +31110,7 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
@@ -33196,7 +33192,7 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
@@ -35158,7 +35154,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
@@ -37894,7 +37890,7 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
@@ -38004,7 +38000,7 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
@@ -41162,7 +41158,7 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">

--- a/output/pdf_financials_xlsx/STR.H.xlsx
+++ b/output/pdf_financials_xlsx/STR.H.xlsx
@@ -1655,11 +1655,15 @@
       <c r="D20" s="3" t="n">
         <v>-1.676561</v>
       </c>
-      <c r="E20" s="3" t="n">
-        <v>3.332285</v>
-      </c>
-      <c r="F20" s="3" t="n">
-        <v>-0.051206</v>
+      <c r="E20" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F20" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G20" s="3" t="n">
         <v>-0.070997</v>
@@ -1719,10 +1723,10 @@
         <v>0</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>0</v>
+        <v>-0.499652</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>0</v>
+        <v>-0.499652</v>
       </c>
       <c r="G21" s="3" t="n">
         <v>0</v>
@@ -4754,19 +4758,19 @@
         <v>0</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.042018</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.008595999999999999</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.010788</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>0.006</v>
       </c>
       <c r="M67" s="3" t="n">
         <v>0</v>
@@ -6787,7 +6791,7 @@
         <v>-1.676561</v>
       </c>
       <c r="E99" s="3" t="n">
-        <v>-0.609874</v>
+        <v>3.332285</v>
       </c>
       <c r="F99" s="3" t="n">
         <v>-0.051206</v>
@@ -6931,13 +6935,13 @@
         <v>0</v>
       </c>
       <c r="K101" s="3" t="n">
-        <v>0</v>
+        <v>-0.000592</v>
       </c>
       <c r="L101" s="3" t="n">
-        <v>0</v>
+        <v>-0.002239</v>
       </c>
       <c r="M101" s="3" t="n">
-        <v>0</v>
+        <v>-0.002239</v>
       </c>
       <c r="N101" s="3" t="n">
         <v>0</v>
@@ -7030,19 +7034,19 @@
         </is>
       </c>
       <c r="B103" s="3" t="n">
-        <v>0</v>
+        <v>-0.002943</v>
       </c>
       <c r="C103" s="3" t="n">
-        <v>0</v>
+        <v>-0.000414</v>
       </c>
       <c r="D103" s="3" t="n">
-        <v>0</v>
+        <v>-0.033061</v>
       </c>
       <c r="E103" s="3" t="n">
-        <v>0</v>
+        <v>0.019275</v>
       </c>
       <c r="F103" s="3" t="n">
-        <v>0</v>
+        <v>0.001875</v>
       </c>
       <c r="G103" s="3" t="n">
         <v>-0.004583</v>
@@ -7225,13 +7229,13 @@
         <v>-1.486043</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>-0.053394</v>
+        <v>-0.086455</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>0.004146</v>
+        <v>0.023421</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>0.00058</v>
+        <v>0.002455</v>
       </c>
       <c r="G106" s="3" t="n">
         <v>-0.008189</v>
@@ -7246,13 +7250,13 @@
         <v>-0.002966</v>
       </c>
       <c r="K106" s="3" t="n">
-        <v>0.005967</v>
+        <v>0.005375</v>
       </c>
       <c r="L106" s="3" t="n">
-        <v>0.058513</v>
+        <v>0.056274</v>
       </c>
       <c r="M106" s="3" t="n">
-        <v>0.061775</v>
+        <v>0.059536</v>
       </c>
       <c r="N106" s="3" t="n">
         <v>0</v>
@@ -7474,13 +7478,13 @@
         <v>0</v>
       </c>
       <c r="C110" s="3" t="n">
-        <v>0</v>
+        <v>0.127895</v>
       </c>
       <c r="D110" s="3" t="n">
-        <v>0</v>
+        <v>0.215755</v>
       </c>
       <c r="E110" s="3" t="n">
-        <v>0</v>
+        <v>0.045025</v>
       </c>
       <c r="F110" s="3" t="n">
         <v>0</v>
@@ -9169,10 +9173,8 @@
       <c r="C135" s="3" t="n">
         <v>-1.512475</v>
       </c>
-      <c r="D135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D135" s="3" t="n">
+        <v>-0.9209580000000001</v>
       </c>
       <c r="E135" s="1" t="inlineStr">
         <is>
@@ -19278,7 +19280,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr"/>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E97" t="inlineStr">
         <is>
           <t>-</t>
@@ -21892,7 +21898,11 @@
           <t>Proceeds from share issuance</t>
         </is>
       </c>
-      <c r="D122" t="inlineStr"/>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E122" t="inlineStr">
         <is>
           <t>-</t>
@@ -23064,11 +23074,7 @@
           <t>Net income (loss) from continuing operations $</t>
         </is>
       </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>NetIncomeFromContinuingOperations</t>
-        </is>
-      </c>
+      <c r="D133" t="inlineStr"/>
       <c r="E133" t="inlineStr">
         <is>
           <t>-</t>
@@ -23494,7 +23500,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr"/>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E137" t="inlineStr">
         <is>
           <t>-</t>
@@ -23802,7 +23812,11 @@
           <t>Prepaid expenses and other current assets</t>
         </is>
       </c>
-      <c r="D140" t="inlineStr"/>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E140" t="inlineStr">
         <is>
           <t>-</t>
@@ -26344,7 +26358,11 @@
           <t>Net cash generated from/(used in) operating activities</t>
         </is>
       </c>
-      <c r="D164" t="inlineStr"/>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E164" t="inlineStr">
         <is>
           <t>-</t>
@@ -28780,7 +28798,11 @@
           <t>Prepaid expenses and other current assets</t>
         </is>
       </c>
-      <c r="D187" t="inlineStr"/>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E187" s="5" t="n">
         <v>-0.002943</v>
       </c>
@@ -39588,7 +39610,11 @@
           <t>Net loss before discontinued operations - - -</t>
         </is>
       </c>
-      <c r="D290" t="inlineStr"/>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E290" t="inlineStr">
         <is>
           <t>-</t>
@@ -39692,7 +39718,11 @@
           <t>Net loss from discontinued operations - - -</t>
         </is>
       </c>
-      <c r="D291" t="inlineStr"/>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E291" t="inlineStr">
         <is>
           <t>-</t>
